--- a/scripts/ground-truth/judah-2026-05-30-oufc.xlsx
+++ b/scripts/ground-truth/judah-2026-05-30-oufc.xlsx
@@ -1,41 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06141CD0-4D7E-4134-897D-EB374D74B3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="29175" yWindow="990" windowWidth="28425" windowHeight="15210" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29175" yWindow="990" windowWidth="28425" windowHeight="15210" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
-    <sheet name="Goals" sheetId="3" r:id="rId3"/>
-    <sheet name="Saves" sheetId="4" r:id="rId4"/>
-    <sheet name="Distribution" sheetId="5" r:id="rId5"/>
-    <sheet name="Crosses" sheetId="6" r:id="rId6"/>
-    <sheet name="Sweeper" sheetId="7" r:id="rId7"/>
-    <sheet name="1v1s" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Metadata" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Goals" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Saves" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Distribution" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Crosses" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Sweeper" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="1v1s" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="212">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -205,6 +191,9 @@
     <t>video_job_id</t>
   </si>
   <si>
+    <t>d173e102-f0d7-4259-84c2-afa23550442a</t>
+  </si>
+  <si>
     <t>Fill in after upload — needed for eval</t>
   </si>
   <si>
@@ -238,6 +227,45 @@
     <t>GK observations</t>
   </si>
   <si>
+    <t>Counter attack</t>
+  </si>
+  <si>
+    <t>Driven</t>
+  </si>
+  <si>
+    <t>6-Yard Box</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>GK Right</t>
+  </si>
+  <si>
+    <t>Open play</t>
+  </si>
+  <si>
+    <t>Central Box</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>GK Left</t>
+  </si>
+  <si>
+    <t>Black couldn't build out of the back, ball taken away, pass into the middle. Player takes an excellent strike that score top right.</t>
+  </si>
+  <si>
+    <t>GK was ready, but didn't dive or attempt for the ball. Misjudged that it was on goal.</t>
+  </si>
+  <si>
+    <t>Right back gives the ball away, opposing player steps right into the box and hammers the ball low right.</t>
+  </si>
+  <si>
+    <t>GK made the pass, but was too central. The bottom right of the net was wide open. No chance.</t>
+  </si>
+  <si>
     <t>Shot origin</t>
   </si>
   <si>
@@ -256,6 +284,189 @@
     <t>Body zone (A/B/C)</t>
   </si>
   <si>
+    <t>6:17</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Catch</t>
+  </si>
+  <si>
+    <t>Held</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Centre</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>Wide Right</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shot came in from out wide, maybe a kick-in. </t>
+  </si>
+  <si>
+    <t>GK was ready for the ball as it was driven in from out wide.</t>
+  </si>
+  <si>
+    <t>18:26</t>
+  </si>
+  <si>
+    <t>Ball finds it way to an unmarked man in the 6 yard box, who shoots low left of the GK</t>
+  </si>
+  <si>
+    <t>Set position, ready to attack, collapses to hold the ball on his left side.</t>
+  </si>
+  <si>
+    <t>19:03</t>
+  </si>
+  <si>
+    <t>Long shot taken from unknown place. High looping that the GK catched.</t>
+  </si>
+  <si>
+    <t>19:56</t>
+  </si>
+  <si>
+    <t>K-Barrier</t>
+  </si>
+  <si>
+    <t>Rebound (dangerous)</t>
+  </si>
+  <si>
+    <t>Player receives a ball in the 6-yard box and shoots low close</t>
+  </si>
+  <si>
+    <t>Aggressive K-barrier block that rebounds into a dangerous spot</t>
+  </si>
+  <si>
+    <t>19:58</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Rebound (safe)</t>
+  </si>
+  <si>
+    <t>Player attacks the rebound but is stopped by the D and GK</t>
+  </si>
+  <si>
+    <t>GK takes another close range shot but rebound goes out safely</t>
+  </si>
+  <si>
+    <t>25:22</t>
+  </si>
+  <si>
+    <t>Unclear where the ball came from</t>
+  </si>
+  <si>
+    <t>GK makes a routine grab</t>
+  </si>
+  <si>
+    <t>31:45</t>
+  </si>
+  <si>
+    <t>Black team gives the ball away in an attempt to switch the ball. Player intercepts and delivers a weak shot on goal.</t>
+  </si>
+  <si>
+    <t>GK was ready for the pass, but was on his toes already and ready for the easy pick up.</t>
+  </si>
+  <si>
+    <t>Kick in sent straight onto goal.</t>
+  </si>
+  <si>
+    <t>GK was on his toes facing the ball and held confidently.</t>
+  </si>
+  <si>
+    <t>Corner Right</t>
+  </si>
+  <si>
+    <t>Punch</t>
+  </si>
+  <si>
+    <t>High corner kick. GK punched/tipped the ball but not very far. Midfielder cleared it.</t>
+  </si>
+  <si>
+    <t>GK was set, strong jump to tip the ball away, but not far enough out of danger.</t>
+  </si>
+  <si>
+    <t>Wide Left</t>
+  </si>
+  <si>
+    <t>Long shot on target, bounced in from of the GK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong pick up off the bounce. </t>
+  </si>
+  <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>Long kick in punched away by the GK</t>
+  </si>
+  <si>
+    <t>Movement off the line to run out and punch the ball away.</t>
+  </si>
+  <si>
+    <t>Deflect</t>
+  </si>
+  <si>
+    <t>Player gives the ball away in the middle of the 6-yard box, easy uncontested shot on goal.</t>
+  </si>
+  <si>
+    <t>GK was in a set position and ready for this 1v1. Pushes the mid height shot wide away from immediate danger.</t>
+  </si>
+  <si>
+    <t>Player receives the ball in the centre of the park, and has a shot on goal.</t>
+  </si>
+  <si>
+    <t>In position, set, and was able to hold the ball driven at him.</t>
+  </si>
+  <si>
+    <t>Central Distance</t>
+  </si>
+  <si>
+    <t>Corner</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Long shot on target away from the GK but on net</t>
+  </si>
+  <si>
+    <t>GK gets a strong push to parry the ball with 2 hands.</t>
+  </si>
+  <si>
+    <t>Corner Left</t>
+  </si>
+  <si>
+    <t>Corner kick punched away</t>
+  </si>
+  <si>
+    <t>Ready and set. Punched the ball away.</t>
+  </si>
+  <si>
+    <t>Coaching moment, keeper should've held it.</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>QUICK TOTALS — fill these IN PLACE OF logging every event if you do not want to tag row-by-row.</t>
   </si>
   <si>
@@ -316,6 +527,93 @@
     <t>First touch</t>
   </si>
   <si>
+    <t>6:23</t>
+  </si>
+  <si>
+    <t>After save</t>
+  </si>
+  <si>
+    <t>Throw</t>
+  </si>
+  <si>
+    <t>Short to defender</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Defender</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>18:19</t>
+  </si>
+  <si>
+    <t>Goal kick</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>Drop-kick</t>
+  </si>
+  <si>
+    <t>Long to forward</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>24:59</t>
+  </si>
+  <si>
+    <t>25:29</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Fake roll to draw a player, then switched direction</t>
+  </si>
+  <si>
+    <t>Mishit</t>
+  </si>
+  <si>
+    <t>Backpass</t>
+  </si>
+  <si>
+    <t>Switch wide</t>
+  </si>
+  <si>
+    <t>Midfielder</t>
+  </si>
+  <si>
+    <t>Great vision. GK looked across to the other side to see if there was an option instead of pass in the original direction</t>
+  </si>
+  <si>
+    <t>Dangerous choice. Opponent was too close to the defender to make that play.</t>
+  </si>
+  <si>
+    <t>Throw-in to GK</t>
+  </si>
+  <si>
+    <t>Ball was out of frame, so the origin of the distribution was unknown</t>
+  </si>
+  <si>
+    <t>Drop-kick was kick long, out of bounds</t>
+  </si>
+  <si>
+    <t>Judah could've looked up to the 2 layer, the midfielder, and find a better pressure release pass than short to the defender</t>
+  </si>
+  <si>
+    <t>Forward didn't get on to the ball and was turned over.</t>
+  </si>
+  <si>
     <t>Side</t>
   </si>
   <si>
@@ -328,6 +626,27 @@
     <t>GK starting pos</t>
   </si>
   <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>Floated</t>
+  </si>
+  <si>
+    <t>Far post</t>
+  </si>
+  <si>
+    <t>On line</t>
+  </si>
+  <si>
+    <t>Punched away</t>
+  </si>
+  <si>
+    <t>Looped</t>
+  </si>
+  <si>
+    <t>6yd</t>
+  </si>
+  <si>
     <t>Action</t>
   </si>
   <si>
@@ -338,352 +657,22 @@
   </si>
   <si>
     <t>Event type</t>
-  </si>
-  <si>
-    <t>6-Yard Box</t>
-  </si>
-  <si>
-    <t>Foot</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Held</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Centre</t>
-  </si>
-  <si>
-    <t>Black team gives the ball away in an attempt to switch the ball. Player intercepts and delivers a weak shot on goal.</t>
-  </si>
-  <si>
-    <t>GK was ready for the pass, but was on his toes already and ready for the easy pick up.</t>
-  </si>
-  <si>
-    <t>6:17</t>
-  </si>
-  <si>
-    <t>Open play</t>
-  </si>
-  <si>
-    <t>Driven</t>
-  </si>
-  <si>
-    <t>Central Box</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>GK Right</t>
-  </si>
-  <si>
-    <t>Black couldn't build out of the back, ball taken away, pass into the middle. Player takes an excellent strike that score top right.</t>
-  </si>
-  <si>
-    <t>GK was ready, but didn't dive or attempt for the ball. Misjudged that it was on goal.</t>
-  </si>
-  <si>
-    <t>Right back gives the ball away, opposing player steps right into the box and hammers the ball low right.</t>
-  </si>
-  <si>
-    <t>GK made the pass, but was too central. The bottom right of the net was wide open. No chance.</t>
-  </si>
-  <si>
-    <t>Mid</t>
-  </si>
-  <si>
-    <t>Wide Right</t>
-  </si>
-  <si>
-    <t>Catch</t>
-  </si>
-  <si>
-    <t>Kick in sent straight onto goal.</t>
-  </si>
-  <si>
-    <t>GK was on his toes facing the ball and held confidently.</t>
-  </si>
-  <si>
-    <t>Corner Right</t>
-  </si>
-  <si>
-    <t>Punch</t>
-  </si>
-  <si>
-    <t>Rebound (dangerous)</t>
-  </si>
-  <si>
-    <t>High corner kick. GK punched/tipped the ball but not very far. Midfielder cleared it.</t>
-  </si>
-  <si>
-    <t>GK was set, strong jump to tip the ball away, but not far enough out of danger.</t>
-  </si>
-  <si>
-    <t>Wide Left</t>
-  </si>
-  <si>
-    <t>Long shot on target, bounced in from of the GK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong pick up off the bounce. </t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>Rebound (safe)</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>GK Left</t>
-  </si>
-  <si>
-    <t>Long kick in punched away by the GK</t>
-  </si>
-  <si>
-    <t>Movement off the line to run out and punch the ball away.</t>
-  </si>
-  <si>
-    <t>Deflect</t>
-  </si>
-  <si>
-    <t>Player gives the ball away in the middle of the 6-yard box, easy uncontested shot on goal.</t>
-  </si>
-  <si>
-    <t>GK was in a set position and ready for this 1v1. Pushes the mid height shot wide away from immediate danger.</t>
-  </si>
-  <si>
-    <t>Player receives the ball in the centre of the park, and has a shot on goal.</t>
-  </si>
-  <si>
-    <t>In position, set, and was able to hold the ball driven at him.</t>
-  </si>
-  <si>
-    <t>Central Distance</t>
-  </si>
-  <si>
-    <t>Corner</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Long shot on target away from the GK but on net</t>
-  </si>
-  <si>
-    <t>GK gets a strong push to parry the ball with 2 hands.</t>
-  </si>
-  <si>
-    <t>Corner Left</t>
-  </si>
-  <si>
-    <t>Corner kick punched away</t>
-  </si>
-  <si>
-    <t>Ready and set. Punched the ball away.</t>
-  </si>
-  <si>
-    <t>Coaching moment, keeper should've held it.</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>After save</t>
-  </si>
-  <si>
-    <t>Throw</t>
-  </si>
-  <si>
-    <t>Short to defender</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Defender</t>
-  </si>
-  <si>
-    <t>Clean</t>
-  </si>
-  <si>
-    <t>Fake roll to draw a player, then switched direction</t>
-  </si>
-  <si>
-    <t>Goal kick</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Drop-kick</t>
-  </si>
-  <si>
-    <t>Long to forward</t>
-  </si>
-  <si>
-    <t>Forward</t>
-  </si>
-  <si>
-    <t>Mishit</t>
-  </si>
-  <si>
-    <t>Backpass</t>
-  </si>
-  <si>
-    <t>Switch wide</t>
-  </si>
-  <si>
-    <t>Midfielder</t>
-  </si>
-  <si>
-    <t>Great vision. GK looked across to the other side to see if there was an option instead of pass in the original direction</t>
-  </si>
-  <si>
-    <t>Dangerous choice. Opponent was too close to the defender to make that play.</t>
-  </si>
-  <si>
-    <t>Throw-in to GK</t>
-  </si>
-  <si>
-    <t>Ball was out of frame, so the origin of the distribution was unknown</t>
-  </si>
-  <si>
-    <t>Drop-kick was kick long, out of bounds</t>
-  </si>
-  <si>
-    <t>Judah could've looked up to the 2 layer, the midfielder, and find a better pressure release pass than short to the defender</t>
-  </si>
-  <si>
-    <t>Forward didn't get on to the ball and was turned over.</t>
-  </si>
-  <si>
-    <t>Looped</t>
-  </si>
-  <si>
-    <t>6yd</t>
-  </si>
-  <si>
-    <t>On line</t>
-  </si>
-  <si>
-    <t>Punched away</t>
-  </si>
-  <si>
-    <t>6:23</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shot came in from out wide, maybe a kick-in. </t>
-  </si>
-  <si>
-    <t>GK was ready for the ball as it was driven in from out wide.</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Floated</t>
-  </si>
-  <si>
-    <t>Far post</t>
-  </si>
-  <si>
-    <t>18:19</t>
-  </si>
-  <si>
-    <t>18:26</t>
-  </si>
-  <si>
-    <t>Ball finds it way to an unmarked man in the 6 yard box, who shoots low left of the GK</t>
-  </si>
-  <si>
-    <t>Set position, ready to attack, collapses to hold the ball on his left side.</t>
-  </si>
-  <si>
-    <t>19:03</t>
-  </si>
-  <si>
-    <t>Long shot taken from unknown place. High looping that the GK catched.</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>19:56</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>Player receives a ball in the 6-yard box and shoots low close</t>
-  </si>
-  <si>
-    <t>K-Barrier</t>
-  </si>
-  <si>
-    <t>Aggressive K-barrier block that rebounds into a dangerous spot</t>
-  </si>
-  <si>
-    <t>19:58</t>
-  </si>
-  <si>
-    <t>Player attacks the rebound but is stopped by the D and GK</t>
-  </si>
-  <si>
-    <t>GK takes another close range shot but rebound goes out safely</t>
-  </si>
-  <si>
-    <t>24:59</t>
-  </si>
-  <si>
-    <t>25:22</t>
-  </si>
-  <si>
-    <t>Unclear where the ball came from</t>
-  </si>
-  <si>
-    <t>GK makes a routine grab</t>
-  </si>
-  <si>
-    <t>25:29</t>
-  </si>
-  <si>
-    <t>31:45</t>
-  </si>
-  <si>
-    <t>Counter attack</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[m]:ss"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -691,8 +680,8 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF333333"/>
       <sz val="11"/>
-      <color rgb="FF333333"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -702,28 +691,22 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <color rgb="FF666666"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="8"/>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -775,23 +758,23 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1130,196 +1113,196 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF666666"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -1330,7 +1313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1341,7 +1324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1352,7 +1335,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1363,7 +1346,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1371,7 +1354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -1379,7 +1362,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1390,7 +1373,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1398,7 +1381,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1406,7 +1389,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1414,7 +1397,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -1422,7 +1405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1430,7 +1413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1438,41 +1421,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B10" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B10">
       <formula1>"U6,U7,U8,U9,U10,U11,U12,U13,U14,U15,U16,U17,U18,Senior"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B5" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B5">
       <formula1>"Home,Away,Neutral"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B6" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B6">
       <formula1>"Match,Friendly,Training"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
   <dimension ref="A1:K199"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1484,44 +1467,44 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="10">
-        <v>0.81111111111111112</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>0.8111111111102218</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1530,24 +1513,24 @@
         <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>2.2569444444444444E-2</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>0.022569444445252884</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1556,30 +1539,30 @@
         <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="J3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>2.5057870370370369E-2</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>0.025057870370801538</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -1588,650 +1571,671 @@
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="J4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B3:B199" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B199">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C3:C199" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B3:B199">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C199">
       <formula1>"Us,Opponent"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D199" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C3:C199">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D199">
       <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E199" xr:uid="{00000000-0002-0000-0200-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D199">
+      <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E199">
       <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F199" xr:uid="{00000000-0002-0000-0200-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E199">
+      <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F199">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G199" xr:uid="{00000000-0002-0000-0200-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F199">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G199">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H199" xr:uid="{00000000-0002-0000-0200-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G199">
+      <formula1>"Top,Mid,Low,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H199">
+      <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H199">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
   <dimension ref="A1:N196"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12" style="9" customWidth="1"/>
+    <col min="1" max="1" width="12" style="8" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -2244,1420 +2248,1449 @@
     <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>110</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="J2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>183</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>190</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" t="s">
         <v>101</v>
       </c>
-      <c r="D4" t="s">
+      <c r="M4" t="s">
         <v>102</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="F4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" t="s">
-        <v>135</v>
-      </c>
-      <c r="J4" t="s">
-        <v>106</v>
-      </c>
-      <c r="K4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L4" t="s">
-        <v>191</v>
-      </c>
-      <c r="M4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>193</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" t="s">
         <v>104</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="J5" t="s">
-        <v>120</v>
-      </c>
-      <c r="K5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>196</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I6" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="J6" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="K6" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="L6" t="s">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>201</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="I7" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="K7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="L7" t="s">
-        <v>202</v>
-      </c>
-      <c r="M7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>205</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J8" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="M8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>209</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s">
+        <v>119</v>
+      </c>
+      <c r="M9" t="s">
         <v>120</v>
       </c>
-      <c r="K9" t="s">
-        <v>107</v>
-      </c>
-      <c r="L9" t="s">
-        <v>108</v>
-      </c>
-      <c r="M9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="8">
-        <v>2.3171296296296294E-2</v>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>0.023171296295913635</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" t="s">
         <v>121</v>
       </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="M10" t="s">
         <v>122</v>
       </c>
-      <c r="G10" t="s">
-        <v>103</v>
-      </c>
-      <c r="H10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" t="s">
-        <v>105</v>
-      </c>
-      <c r="J10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K10" t="s">
-        <v>107</v>
-      </c>
-      <c r="L10" t="s">
-        <v>123</v>
-      </c>
-      <c r="M10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="8">
-        <v>2.6435185185185183E-2</v>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>0.02643518518380006</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11" t="s">
         <v>125</v>
       </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="M11" t="s">
         <v>126</v>
       </c>
-      <c r="G11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" t="s">
-        <v>127</v>
-      </c>
-      <c r="J11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L11" t="s">
-        <v>128</v>
-      </c>
-      <c r="M11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>2.8726851851851851E-2</v>
+        <v>0.028726851851388346</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J12" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="8">
-        <v>3.0983796296296294E-2</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>0.030983796295913635</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" t="s">
         <v>130</v>
       </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" t="s">
-        <v>133</v>
-      </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="I13" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="K13" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="L13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="M13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
-        <v>3.2615740740740737E-2</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>0.03261574073985685</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M14" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="8">
-        <v>3.3391203703703701E-2</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>0.033391203702194616</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" t="s">
+        <v>97</v>
+      </c>
+      <c r="K15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" t="s">
         <v>134</v>
       </c>
-      <c r="I15" t="s">
+      <c r="M15" t="s">
         <v>135</v>
       </c>
-      <c r="J15" t="s">
-        <v>120</v>
-      </c>
-      <c r="K15" t="s">
-        <v>107</v>
-      </c>
-      <c r="L15" t="s">
-        <v>140</v>
-      </c>
-      <c r="M15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
-        <v>3.3854166666666664E-2</v>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>0.033854166667879326</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J16" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K16" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L16" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="M16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="8">
-        <v>3.4224537037037039E-2</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>0.03422453703751671</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K17" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M17" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
-        <v>3.439814814814815E-2</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>0.03439814814919373</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J18" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="K18" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="L18" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>3.4629629629629628E-2</v>
+        <v>0.034629629630217096</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="I19" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J19" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L19" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M19" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="N19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>3.7662037037037036E-2</v>
+        <v>0.037662037037080154</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K20" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>3.8564814814814816E-2</v>
+        <v>0.03856481481489027</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="7"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="7"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="7"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="7"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="7"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="7"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="7"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="7"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="7"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" s="7"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" s="7"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" s="7"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" s="7"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="7"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" s="7"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" s="7"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" s="7"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="7"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" s="7"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="7"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" s="7"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" s="7"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" s="7"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="7"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" s="7"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" s="7"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" s="7"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" s="7"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" s="7"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" s="7"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" s="7"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" s="7"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" s="7"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="7"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="7"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="7"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="7"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="7"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="7"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="7"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="7"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="7"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" s="7"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" s="7"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" s="7"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" s="7"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" s="7"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" s="7"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" s="7"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="7"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" s="7"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" s="7"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" s="7"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" s="7"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" s="7"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="7"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" s="7"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" s="7"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" s="7"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" s="7"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" s="7"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" s="7"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" s="7"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" s="7"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" s="7"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" s="7"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" s="7"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" s="7"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" s="7"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" s="7"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A102" s="7"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" s="7"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A104" s="7"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A105" s="7"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A106" s="7"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" s="7"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A108" s="7"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" s="7"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A110" s="7"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A111" s="7"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A112" s="7"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A113" s="7"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A114" s="7"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A115" s="7"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A116" s="7"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A117" s="7"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" s="7"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A119" s="7"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" s="7"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A121" s="7"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A122" s="7"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A123" s="7"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A124" s="7"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A125" s="7"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A126" s="7"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A127" s="7"/>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A128" s="7"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A129" s="7"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" s="7"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A131" s="7"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" s="7"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A133" s="7"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A134" s="7"/>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A135" s="7"/>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A136" s="7"/>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A137" s="7"/>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A138" s="7"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A139" s="7"/>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A140" s="7"/>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A141" s="7"/>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A142" s="7"/>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A143" s="7"/>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A144" s="7"/>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A145" s="7"/>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A146" s="7"/>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A147" s="7"/>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A148" s="7"/>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A149" s="7"/>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A150" s="7"/>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A151" s="7"/>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A152" s="7"/>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A153" s="7"/>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A154" s="7"/>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A155" s="7"/>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A156" s="7"/>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A157" s="7"/>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A158" s="7"/>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A159" s="7"/>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A160" s="7"/>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A161" s="7"/>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A162" s="7"/>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A163" s="7"/>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A164" s="7"/>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A165" s="7"/>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A166" s="7"/>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A167" s="7"/>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A168" s="7"/>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A169" s="7"/>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A170" s="7"/>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A171" s="7"/>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A172" s="7"/>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A173" s="7"/>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A174" s="7"/>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A175" s="7"/>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A176" s="7"/>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A177" s="7"/>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A178" s="7"/>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A179" s="7"/>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A180" s="7"/>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A181" s="7"/>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A182" s="7"/>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A183" s="7"/>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A184" s="7"/>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A185" s="7"/>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A186" s="7"/>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A187" s="7"/>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A188" s="7"/>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A189" s="7"/>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A190" s="7"/>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A191" s="7"/>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A192" s="7"/>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A193" s="7"/>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A194" s="7"/>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A195" s="7"/>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A196" s="7"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="9"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="9"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="9"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="9"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="9"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="9"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="9"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="9"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="9"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="9"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="9"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="9"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="9"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="9"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="9"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="9"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="9"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="9"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="9"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="9"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="9"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="9"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="9"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="9"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="9"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="9"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="9"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="9"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="9"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="9"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="9"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="9"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="9"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="9"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="9"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="9"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="9"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="9"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="9"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="9"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="9"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="9"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="9"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="9"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="9"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="9"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="9"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="9"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="9"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="9"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="9"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="9"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="9"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="9"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="9"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="9"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="9"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="9"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="9"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="9"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="9"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="9"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="9"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="9"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="9"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="9"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="9"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="9"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="9"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="9"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="9"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="9"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="9"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="9"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="9"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="9"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="9"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="9"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="9"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="9"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="9"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="9"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="9"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="9"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="9"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="9"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="9"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="9"/>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="9"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="9"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="9"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="9"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="9"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="9"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="9"/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="9"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="9"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="9"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="9"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="9"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="9"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="9"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="9"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="9"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="9"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="9"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="9"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="9"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="9"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="9"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="9"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="9"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="9"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="9"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="9"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="9"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="9"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="9"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="9"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="9"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="9"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="9"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="9"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="9"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="9"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="9"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="9"/>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="9"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="9"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="9"/>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="9"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="9"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="9"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="9"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="9"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="9"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="9"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="9"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="9"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="9"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H196" xr:uid="{00000000-0002-0000-0300-00000C000000}">
+  <dataValidations count="20">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B196">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B2:B196">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C196">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C196">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D196">
+      <formula1>"Foot,Header,Deflection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D196">
+      <formula1>"Foot,Header,Deflection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E196">
+      <formula1>"Yes,No,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E2:E196">
+      <formula1>"Yes,No,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F196">
+      <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F2:F196">
+      <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G196">
+      <formula1>"Yes,Partial,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G196">
+      <formula1>"Yes,Partial,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H196">
       <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C196" xr:uid="{00000000-0002-0000-0300-000002000000}">
-      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D196" xr:uid="{00000000-0002-0000-0300-000004000000}">
-      <formula1>"Foot,Header,Deflection"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E196" xr:uid="{00000000-0002-0000-0300-000006000000}">
-      <formula1>"Yes,No,Unclear"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F196" xr:uid="{00000000-0002-0000-0300-000008000000}">
-      <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G196" xr:uid="{00000000-0002-0000-0300-00000A000000}">
-      <formula1>"Yes,Partial,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I196" xr:uid="{00000000-0002-0000-0300-00000E000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H196">
+      <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I196">
       <formula1>"A,B,C,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J196" xr:uid="{00000000-0002-0000-0300-000010000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I196">
+      <formula1>"A,B,C,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J10:J196">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K196" xr:uid="{00000000-0002-0000-0300-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J196">
+      <formula1>"Top,Mid,Low,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:K196">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B196" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="K2:K196">
+      <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
   <dimension ref="A1:K199"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3672,1323 +3705,1323 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H17" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I17" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J17" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
-        <v>189</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>175</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F19" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G19" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H19" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>204</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H20" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I20" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J20" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
-        <v>208</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>183</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>2.210648148148148E-2</v>
+        <v>0.022106481483206153</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H22" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I22" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J22" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K22" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>2.2291666666666664E-2</v>
+        <v>0.022291666668024845</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H23" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="8">
-        <v>2.3194444444444441E-2</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>0.02319444444583496</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H24" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I24" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>2.4097222222222221E-2</v>
+        <v>0.024097222223645076</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I25" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="J25" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>2.4837962962962961E-2</v>
+        <v>0.024837962962919846</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H26" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I26" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>2.4999999999999998E-2</v>
+        <v>0.02500000000145519</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>2.7453703703703702E-2</v>
+        <v>0.027453703703940846</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>2.8807870370370369E-2</v>
+        <v>0.02880787037065602</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="H29" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="J29" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>3.2627314814814817E-2</v>
+        <v>0.03262731481299852</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H30" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I30" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J30" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>3.3321759259259259E-2</v>
+        <v>0.033321759259706596</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" t="s">
         <v>173</v>
       </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" t="s">
-        <v>156</v>
-      </c>
-      <c r="H31" t="s">
-        <v>157</v>
-      </c>
-      <c r="I31" t="s">
-        <v>158</v>
-      </c>
       <c r="J31" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
-        <v>3.3622685185185186E-2</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
+        <v>0.03362268518685596</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H32" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J32" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K32" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>3.3888888888888885E-2</v>
+        <v>0.03388888888730435</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E33" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G33" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="K33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>3.4282407407407407E-2</v>
+        <v>0.03428240740686306</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J34" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>3.7210648148148145E-2</v>
+        <v>0.037210648148175096</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H35" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J35" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>3.7499999999999999E-2</v>
+        <v>0.03749999999854481</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H36" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J36" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>3.7696759259259256E-2</v>
+        <v>0.03769675926014315</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H37" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="J37" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K37" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A38" s="8">
-        <v>3.8634259259259257E-2</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="10">
+        <v>0.03863425926101627</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E38" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F38" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H38" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I38" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="K38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
   </sheetData>
@@ -4996,44 +5029,68 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" sqref="B17:B199" xr:uid="{00000000-0002-0000-0400-000000000000}">
+  <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" sqref="B100:B199">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C17:C199" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B17:B199">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C100:C199">
       <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17:D199" xr:uid="{00000000-0002-0000-0400-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C17:C199">
+      <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D100:D199">
       <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E17:F199" xr:uid="{00000000-0002-0000-0400-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D17:D199">
+      <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E100:F199">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G17:G199" xr:uid="{00000000-0002-0000-0400-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E17:F199">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G100:G199">
       <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H17:H199" xr:uid="{00000000-0002-0000-0400-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G17:G199">
+      <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H100:H199">
       <formula1>"Left,Centre,Right,Backwards"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I17:I199" xr:uid="{00000000-0002-0000-0400-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H17:H199">
+      <formula1>"Left,Centre,Right,Backwards"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I100:I199">
       <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J17:J199" xr:uid="{00000000-0002-0000-0400-00000E000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I17:I199">
+      <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J100:J199">
+      <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J17:J199">
       <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFF97316"/>
   </sheetPr>
   <dimension ref="A1:I198"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -5044,754 +5101,781 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>198</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="H2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="8">
-        <v>1.8211736111111109E-2</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>0.018211736110970378</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G3" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="H3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="8">
-        <v>1.8217418981481479E-2</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>0.01821741898311302</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="H4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="8">
-        <v>3.7662037037037036E-2</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>0.037662037037080154</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="H5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B2 B5:B198" xr:uid="{00000000-0002-0000-0500-000000000000}">
+  <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B198">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2 C5:C198" xr:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B5:B198">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C198">
       <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D198" xr:uid="{00000000-0002-0000-0500-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2">
+      <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C5:C198">
+      <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D198">
       <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E198" xr:uid="{00000000-0002-0000-0500-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D198">
+      <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E198">
       <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F198" xr:uid="{00000000-0002-0000-0500-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E198">
+      <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F198">
       <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G198" xr:uid="{00000000-0002-0000-0500-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F198">
+      <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G198">
       <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H198" xr:uid="{00000000-0002-0000-0500-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G198">
+      <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H198">
+      <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H198">
       <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFA78BFA"/>
   </sheetPr>
   <dimension ref="A1:H202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -5803,668 +5887,686 @@
     <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>97</v>
+        <v>208</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0600-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0600-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"Clearance,Interception,Tackle,Header"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0600-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Clearance,Interception,Tackle,Header"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202" xr:uid="{00000000-0002-0000-0600-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+      <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202" xr:uid="{00000000-0002-0000-0600-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"None,1 attacker,2+ attackers"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202" xr:uid="{00000000-0002-0000-0600-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+      <formula1>"None,1 attacker,2+ attackers"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
+      <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD4A853"/>
   </sheetPr>
   <dimension ref="A1:E202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -6473,639 +6575,648 @@
     <col min="5" max="5" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0700-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0700-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0700-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+      <formula1>"Won,Conceded,Saved,Cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
       <formula1>"Won,Conceded,Saved,Cleared"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>